--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Accessibility" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -28,28 +29,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001B2A4A"/>
+      <color rgb="FF1B2A4A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="008B4A4A"/>
+      <color rgb="FF8B4A4A"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -61,17 +72,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C5F8A"/>
+        <fgColor rgb="FF2C5F8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
+        <fgColor rgb="FF1B2A4A"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,9 +115,14 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -181,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q188" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q212" headerRowCount="1">
   <autoFilter ref="A1:Q188"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
@@ -202,7 +218,7 @@
     <tableColumn id="16" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="17" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -226,7 +242,7 @@
     <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="15" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -520,28 +536,28 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" style="11" min="1" max="1"/>
+    <col width="95" customWidth="1" style="11" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1" s="11">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NRC - NGA MSNA 2026 accessibility report</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.6" customHeight="1" s="11">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="11">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>This file lists every ward (and, on the second sheet, every individual cluster) currently assigned to your organisation under the NGA MSNA 2026 sampling design, so you can tell us where your teams are having trouble collecting data and why. We use this to decide how to respond - drawing a replacement cluster where needed - and to correctly document, in our final reporting, which areas' we were able to collect from and which we weren't. Accurate, complete reporting from you feeds directly into that documentation.</t>
         </is>
@@ -554,84 +570,84 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.6" customHeight="1" s="11">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="60" customHeight="1" s="11">
       <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Open the 'Ward Accessibility' sheet first - this is your main report, one row per ward you have clusters in. It's pre-filled with every ward/LGA combination assigned to you; you don't need to add or remove rows. Rows are sorted within each LGA by Total target HHs, largest first, so your main wards come before any small border cases.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="60" customHeight="1" s="11">
       <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="60" customHeight="1" s="11">
       <c r="A11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="60" customHeight="1" s="11">
       <c r="A12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="60" customHeight="1" s="11">
       <c r="A13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="60" customHeight="1" s="11">
       <c r="A14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="60" customHeight="1" s="11">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="90" customHeight="1">
+    <row r="16" ht="90" customHeight="1" s="11">
       <c r="A16" s="5" t="n">
         <v>8</v>
       </c>
@@ -641,7 +657,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15.6" customHeight="1" s="11">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
@@ -660,25 +676,25 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="45" customHeight="1" s="11">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="45" customHeight="1" s="11">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -698,26 +714,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q188"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q212"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" style="11" min="1" max="2"/>
+    <col width="16" customWidth="1" style="11" min="3" max="3"/>
+    <col width="19" customWidth="1" style="11" min="4" max="4"/>
+    <col width="30" customWidth="1" style="11" min="5" max="6"/>
+    <col width="14" customWidth="1" style="11" min="7" max="7"/>
+    <col width="20" customWidth="1" style="11" min="8" max="8"/>
+    <col width="16" customWidth="1" style="11" min="9" max="9"/>
+    <col width="30" customWidth="1" style="11" min="10" max="10"/>
+    <col width="20" customWidth="1" style="11" min="11" max="11"/>
+    <col width="19" customWidth="1" style="11" min="12" max="12"/>
+    <col width="16" customWidth="1" style="11" min="13" max="13"/>
+    <col width="30" customWidth="1" style="11" min="14" max="14"/>
+    <col width="17" customWidth="1" style="11" min="15" max="15"/>
+    <col width="30" customWidth="1" style="11" min="16" max="16"/>
+    <col width="18" customWidth="1" style="11" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +919,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1027,12 +1041,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1149,12 +1163,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1271,12 +1285,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1332,12 +1346,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,12 +1407,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1637,12 +1651,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1698,12 +1712,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1759,12 +1773,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1820,12 +1834,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1881,12 +1895,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1942,12 +1956,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2003,12 +2017,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2064,12 +2078,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2125,12 +2139,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2501,12 +2515,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2623,12 +2637,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2816,12 +2830,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6625,12 +6639,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -6686,12 +6700,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8413,12 +8427,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Physical access (terrain, flooding, roads)</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -8677,12 +8691,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -8799,12 +8813,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -8860,12 +8874,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -8921,12 +8935,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -8982,12 +8996,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -9043,12 +9057,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10241,12 +10255,12 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10434,12 +10448,12 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -10495,12 +10509,12 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Insecurity / conflict</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12120,12 +12134,17 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -12181,12 +12200,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -12242,12 +12266,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -12303,12 +12332,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -12364,12 +12398,17 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -12425,12 +12464,17 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -12496,12 +12540,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -12557,12 +12606,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -12618,12 +12672,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -12679,12 +12738,17 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>N/A - fully accessible</t>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -12740,43 +12804,1046 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Maiha Gari</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" s="12" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sina Kamale</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" s="12" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Duvu</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="12" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Kwaja</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="12" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Bwalki</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="12" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ashigashiya</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="12" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Chikide Jahode</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="12" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Hambagda</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>7</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>30</v>
+      </c>
+      <c r="O196" s="12" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Kurunabasa Ngoshe Sama</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Kuranabasa</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>6</v>
+      </c>
+      <c r="O197" s="12" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Khaddamari</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" s="12" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tuba</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="12" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ajiri</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Ajiri</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>N/A - fully accessible</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>WhatsApp/verbal (coordinator-transcribed)</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>6</v>
+      </c>
+      <c r="O200" s="12" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Kawuri</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="12" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Yajiwa</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" s="12" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Sugum Tagali</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="12" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Kilange Funa</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Gombi South</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Hong; Song</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>6</v>
+      </c>
+      <c r="O204" s="12" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sigire</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Gaanda</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="O205" s="12" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Digil</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Hildi</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>5</v>
+      </c>
+      <c r="O206" s="12" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Guyaku</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" s="12" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Hussari Tampul</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Uba</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>4</v>
+      </c>
+      <c r="O208" s="12" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Kilange Funa</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Daksiri</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Gombi; Song</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>2</v>
+      </c>
+      <c r="O209" s="12" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Gundo</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Bare</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Shelleng</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>6</v>
+      </c>
+      <c r="O210" s="12" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Soye</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Wala Warabe</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Bama</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>2</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>5</v>
+      </c>
+      <c r="O211" s="12" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Abbaram</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kawuri</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Bama; Dikwa</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>2</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>10</v>
+      </c>
+      <c r="O212" s="12" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="K2:K188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="K2:K188 K189:K203 K204:K212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L188 L189:L203 L204:L212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P188 P189:P203 P204:P212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q188" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q188 Q189:Q203 Q204:Q212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O189:O203 O204:O212" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12793,23 +13860,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O326"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" style="11" min="1" max="2"/>
+    <col width="16" customWidth="1" style="11" min="3" max="3"/>
+    <col width="14" customWidth="1" style="11" min="4" max="5"/>
+    <col width="16" customWidth="1" style="11" min="6" max="6"/>
+    <col width="24" customWidth="1" style="11" min="7" max="7"/>
+    <col width="15" customWidth="1" style="11" min="8" max="8"/>
+    <col width="20" customWidth="1" style="11" min="9" max="9"/>
+    <col width="19" customWidth="1" style="11" min="10" max="10"/>
+    <col width="16" customWidth="1" style="11" min="11" max="11"/>
+    <col width="30" customWidth="1" style="11" min="12" max="12"/>
+    <col width="17" customWidth="1" style="11" min="13" max="13"/>
+    <col width="30" customWidth="1" style="11" min="14" max="14"/>
+    <col width="18" customWidth="1" style="11" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25828,22 +26893,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4868952-7E7A-4B39-92B9-04B32A01D02B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFCB546C-BF53-4BBB-835F-74F284B720A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26219879-FEA8-414F-AEC2-9E0903E8DC91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AFF8548-5196-48D4-8CDD-20DBE29B4379}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDAE2783-7C8D-43D8-8FC7-AE841493D549}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA554F62-A076-4296-8961-90957729E29F}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -197,8 +197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q212" headerRowCount="1">
-  <autoFilter ref="A1:Q188"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q352" headerRowCount="1">
+  <autoFilter ref="A1:Q352"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q212"/>
+  <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="11" min="1" max="2"/>
@@ -13622,7 +13622,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>Newly added 2026-09-16 - not previously listed.</t>
@@ -13827,23 +13826,5694 @@
       </c>
       <c r="O212" s="12" t="n"/>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Dirma</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Shelleng; Song</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Gudu Mboi</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Gwapopolok</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Shelleng</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Kwajaffa</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Ngohi</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Puba Vidau</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Thilbang</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Hong; Song</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Betso</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Michika; Mubi North</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Hausari Zadawa</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Humbutudi</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Maiha; Mubi South</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Manjekin</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Mayo Bani</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Mugulbu</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Maiha; Mubi South</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Ngohi</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Uvu Uda</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Yelwa</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Mubi North; Mubi South; Yola North</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Zumo</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Fufore; Maiha; Song</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Bambam</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Bare</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Chikila</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Guyuk</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Dadiya</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Gamadiyo</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Gundo</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Demsa; Guyuk; Numan; Shelleng</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Imburu</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Jen Ardido</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Jen Kaigama</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Kindiyo</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Guyuk</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Kodomti</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Demsa; Numan</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Kola</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Guyuk; Shelleng</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Mona</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Nyuwar / Jessu</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Guyuk</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Vulpi</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Farang</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Fufore; Song</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Hoserezum</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Hong; Mubi South; Song</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Mugulbu</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Hong; Mubi South</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Betso</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Hong; Mubi North</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Dille Huyim</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Duhu</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Hussari Tampul</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Hong; Mubi North</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Kirchinga</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Mijilu</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ngurthavu Kopa</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Pallam</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Madagali</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Hussari Tampul</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Hong; Michika</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Mayo Lope</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Hong; Mubi South</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Uba</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Zah</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Hoserezum</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Hong; Maiha; Song</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Humbutudi</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Hong; Maiha</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Mayo Lope</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Hong; Mubi North</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Vimtim</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Dilli</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Demsa</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Dobeli</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Demsa</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Demsa</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Dwam</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Demsa</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Gyawana</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Guyuk; Lamurde</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Kiri</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Shelleng</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Kpasham</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Demsa; Mayo-Belwa</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Waduku</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Damare</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Girei; Yola South</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Beti</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Fufore; Jada</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Dakri</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Girei</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Damare</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Girei; Yola North</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Fufore</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Fufore; Girei</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Girei; Yola North</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Jambutu</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Mayo Inne</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Fufore; Jada; Mayo-Belwa</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Ndikong</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Demsa; Fufore; Mayo-Belwa</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Uki Tuki</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Fufore</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Gulak</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Hyambula</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Waga-Chakawa</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Yabal</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Bama; Konduga; Mafa</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Bolori 2</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Dalwa</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Damboa; Konduga</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Gwange 1</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Gwange 2</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Gwange 3</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Lamisula</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Loskuri</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Konduga; Mafa</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Maisandari</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Masu</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Mafa; Monguno; Nganzai</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Yajiwa</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Konduga; Maiduguri</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Alau</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Bego Yerwa</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Bama; Damboa; Gwoza</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Bolori 1</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Maiduguri</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Borgozo</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Dala</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Jere; Maiduguri</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Foi</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Damboa; Kaga</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Gajiganna</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Magumeri; Nganzai</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Gawa</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Dikwa; Mafa</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Goniri</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Bama</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Hoyo Chingua</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Kalizoram</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Magumeri</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Karagawaru</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Kaga; Magumeri</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Kasugula</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Bama</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Loskuri</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Jere; Mafa</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Mafa; Magumeri</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>0</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Mainok</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Mairi</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Jere; Maiduguri</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Mulgoi Kobchi</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Damboa</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Shehuri</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Bama; Ngala</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Tamsum Gamdua</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Jere; Mafa</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Titiwa</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Magumeri; Nganzai</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Tobolo</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Kaga</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Tuba</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Jere; Nganzai</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Garbagal</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Garin Gawo</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Karasuwa</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Girgir / Bayam</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Jakusko</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Gogaram</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Jakusko</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Jaba</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Bursari; Jakusko</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Jaji Maji</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Karasuwa</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Jawa Garun Dole</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Bursari</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Jawur / Katamma</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Bursari; Jakusko</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Kadira</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Jakusko</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Zabudum / Dachia</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Jakusko</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Goduram</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Tarmua</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Fune; Gujba</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Mashio</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Fune</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Ngamdu</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Ngelzarma A</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Fune</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Ngelzarma B</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Fune</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ngurbuwa</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Sungul Koka</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Tarmua</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>0</v>
+      </c>
+      <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Ajigin A</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ajigin B</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Dokshi</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Gulani</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Gabai</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Fika; Gulani</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Gambir Moduri</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>0</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Maisandari / Waziri Ibrahim</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Ngamdu</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Shetimare</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Turmi Malori</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Fika; Fune</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Gujba</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Zangaya Mazawaun</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Fika; Gulani</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K188 K189:K203 K204:K212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L188 L189:L203 L204:L212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P188 P189:P203 P204:P212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q188 Q189:Q203 Q204:Q212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O189:O203 O204:O212" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+    <dataValidation sqref="O2:O352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26902,13 +32572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFCB546C-BF53-4BBB-835F-74F284B720A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EB965D5-B48E-4FEC-BDF8-85F10B2DACAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AFF8548-5196-48D4-8CDD-20DBE29B4379}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760F032D-81B8-45D7-AF25-0839B9CBB247}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA554F62-A076-4296-8961-90957729E29F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C528BE07-F79E-46E2-9885-0796D57EA7B3}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O326" headerRowCount="1">
-  <autoFilter ref="A1:O326"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O487" headerRowCount="1">
+  <autoFilter ref="A1:O487"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -538,26 +538,26 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="30" customWidth="1" style="11" min="1" max="1"/>
-    <col width="95" customWidth="1" style="11" min="2" max="2"/>
+    <col width="30" customWidth="1" style="12" min="1" max="1"/>
+    <col width="95" customWidth="1" style="12" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="11">
+    <row r="1" ht="18" customHeight="1" s="12">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NRC - NGA MSNA 2026 accessibility report</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" s="11">
+    <row r="3" ht="15.6" customHeight="1" s="12">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="11">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="12">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>This file lists every ward (and, on the second sheet, every individual cluster) currently assigned to your organisation under the NGA MSNA 2026 sampling design, so you can tell us where your teams are having trouble collecting data and why. We use this to decide how to respond - drawing a replacement cluster where needed - and to correctly document, in our final reporting, which areas' we were able to collect from and which we weren't. Accurate, complete reporting from you feeds directly into that documentation.</t>
         </is>
@@ -570,84 +570,84 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.6" customHeight="1" s="11">
+    <row r="8" ht="15.6" customHeight="1" s="12">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="11">
+    <row r="9" ht="60" customHeight="1" s="12">
       <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Open the 'Ward Accessibility' sheet first - this is your main report, one row per ward you have clusters in. It's pre-filled with every ward/LGA combination assigned to you; you don't need to add or remove rows. Rows are sorted within each LGA by Total target HHs, largest first, so your main wards come before any small border cases.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="11">
+    <row r="10" ht="60" customHeight="1" s="12">
       <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="11">
+    <row r="11" ht="60" customHeight="1" s="12">
       <c r="A11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" s="11">
+    <row r="12" ht="60" customHeight="1" s="12">
       <c r="A12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="11">
+    <row r="13" ht="60" customHeight="1" s="12">
       <c r="A13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" s="11">
+    <row r="14" ht="60" customHeight="1" s="12">
       <c r="A14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" s="11">
+    <row r="15" ht="60" customHeight="1" s="12">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="90" customHeight="1" s="11">
+    <row r="16" ht="90" customHeight="1" s="12">
       <c r="A16" s="5" t="n">
         <v>8</v>
       </c>
@@ -657,7 +657,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.6" customHeight="1" s="11">
+    <row r="18" ht="15.6" customHeight="1" s="12">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
@@ -676,25 +676,25 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1" s="11">
+    <row r="20" ht="45" customHeight="1" s="12">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1" s="11">
+    <row r="21" ht="45" customHeight="1" s="12">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -717,21 +717,21 @@
   <dimension ref="A1:Q352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="19" customWidth="1" style="11" min="4" max="4"/>
-    <col width="30" customWidth="1" style="11" min="5" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="20" customWidth="1" style="11" min="8" max="8"/>
-    <col width="16" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
-    <col width="20" customWidth="1" style="11" min="11" max="11"/>
-    <col width="19" customWidth="1" style="11" min="12" max="12"/>
-    <col width="16" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="17" customWidth="1" style="11" min="15" max="15"/>
-    <col width="30" customWidth="1" style="11" min="16" max="16"/>
-    <col width="18" customWidth="1" style="11" min="17" max="17"/>
+    <col width="14" customWidth="1" style="12" min="1" max="2"/>
+    <col width="16" customWidth="1" style="12" min="3" max="3"/>
+    <col width="19" customWidth="1" style="12" min="4" max="4"/>
+    <col width="30" customWidth="1" style="12" min="5" max="6"/>
+    <col width="14" customWidth="1" style="12" min="7" max="7"/>
+    <col width="20" customWidth="1" style="12" min="8" max="8"/>
+    <col width="16" customWidth="1" style="12" min="9" max="9"/>
+    <col width="30" customWidth="1" style="12" min="10" max="10"/>
+    <col width="20" customWidth="1" style="12" min="11" max="11"/>
+    <col width="19" customWidth="1" style="12" min="12" max="12"/>
+    <col width="16" customWidth="1" style="12" min="13" max="13"/>
+    <col width="30" customWidth="1" style="12" min="14" max="14"/>
+    <col width="17" customWidth="1" style="12" min="15" max="15"/>
+    <col width="30" customWidth="1" style="12" min="16" max="16"/>
+    <col width="18" customWidth="1" style="12" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12868,7 +12868,7 @@
       <c r="J189" t="n">
         <v>0</v>
       </c>
-      <c r="O189" s="12" t="n"/>
+      <c r="O189" s="10" t="n"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12905,7 +12905,7 @@
       <c r="J190" t="n">
         <v>0</v>
       </c>
-      <c r="O190" s="12" t="n"/>
+      <c r="O190" s="10" t="n"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12942,7 +12942,7 @@
       <c r="J191" t="n">
         <v>0</v>
       </c>
-      <c r="O191" s="12" t="n"/>
+      <c r="O191" s="10" t="n"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12979,7 +12979,7 @@
       <c r="J192" t="n">
         <v>0</v>
       </c>
-      <c r="O192" s="12" t="n"/>
+      <c r="O192" s="10" t="n"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13016,7 +13016,7 @@
       <c r="J193" t="n">
         <v>0</v>
       </c>
-      <c r="O193" s="12" t="n"/>
+      <c r="O193" s="10" t="n"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13053,7 +13053,7 @@
       <c r="J194" t="n">
         <v>0</v>
       </c>
-      <c r="O194" s="12" t="n"/>
+      <c r="O194" s="10" t="n"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13090,7 +13090,7 @@
       <c r="J195" t="n">
         <v>0</v>
       </c>
-      <c r="O195" s="12" t="n"/>
+      <c r="O195" s="10" t="n"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13132,7 +13132,7 @@
       <c r="J196" t="n">
         <v>30</v>
       </c>
-      <c r="O196" s="12" t="n"/>
+      <c r="O196" s="10" t="n"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13174,7 +13174,7 @@
       <c r="J197" t="n">
         <v>6</v>
       </c>
-      <c r="O197" s="12" t="n"/>
+      <c r="O197" s="10" t="n"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13211,7 +13211,7 @@
       <c r="J198" t="n">
         <v>0</v>
       </c>
-      <c r="O198" s="12" t="n"/>
+      <c r="O198" s="10" t="n"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13248,7 +13248,7 @@
       <c r="J199" t="n">
         <v>0</v>
       </c>
-      <c r="O199" s="12" t="n"/>
+      <c r="O199" s="10" t="n"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13295,7 +13295,7 @@
       <c r="J200" t="n">
         <v>6</v>
       </c>
-      <c r="O200" s="12" t="n"/>
+      <c r="O200" s="10" t="n"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13332,7 +13332,7 @@
       <c r="J201" t="n">
         <v>0</v>
       </c>
-      <c r="O201" s="12" t="n"/>
+      <c r="O201" s="10" t="n"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13369,7 +13369,7 @@
       <c r="J202" t="n">
         <v>0</v>
       </c>
-      <c r="O202" s="12" t="n"/>
+      <c r="O202" s="10" t="n"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13406,7 +13406,7 @@
       <c r="J203" t="n">
         <v>0</v>
       </c>
-      <c r="O203" s="12" t="n"/>
+      <c r="O203" s="10" t="n"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13453,7 +13453,7 @@
       <c r="J204" t="n">
         <v>6</v>
       </c>
-      <c r="O204" s="12" t="n"/>
+      <c r="O204" s="10" t="n"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13500,7 +13500,7 @@
       <c r="J205" t="n">
         <v>3</v>
       </c>
-      <c r="O205" s="12" t="n"/>
+      <c r="O205" s="10" t="n"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13547,7 +13547,7 @@
       <c r="J206" t="n">
         <v>5</v>
       </c>
-      <c r="O206" s="12" t="n"/>
+      <c r="O206" s="10" t="n"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13594,7 +13594,7 @@
       <c r="J207" t="n">
         <v>3</v>
       </c>
-      <c r="O207" s="12" t="n"/>
+      <c r="O207" s="10" t="n"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13636,7 +13636,7 @@
       <c r="J208" t="n">
         <v>4</v>
       </c>
-      <c r="O208" s="12" t="n"/>
+      <c r="O208" s="10" t="n"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13683,7 +13683,7 @@
       <c r="J209" t="n">
         <v>2</v>
       </c>
-      <c r="O209" s="12" t="n"/>
+      <c r="O209" s="10" t="n"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13730,7 +13730,7 @@
       <c r="J210" t="n">
         <v>6</v>
       </c>
-      <c r="O210" s="12" t="n"/>
+      <c r="O210" s="10" t="n"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13777,7 +13777,7 @@
       <c r="J211" t="n">
         <v>5</v>
       </c>
-      <c r="O211" s="12" t="n"/>
+      <c r="O211" s="10" t="n"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13824,7 +13824,7 @@
       <c r="J212" t="n">
         <v>10</v>
       </c>
-      <c r="O212" s="12" t="n"/>
+      <c r="O212" s="10" t="n"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14052,7 +14052,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14130,7 +14129,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14249,7 +14247,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14491,7 +14488,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14610,7 +14606,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14729,7 +14724,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14889,7 +14883,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -14926,7 +14919,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -15086,7 +15078,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -15369,7 +15360,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -15529,7 +15519,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -16837,7 +16826,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -16874,7 +16862,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -18387,7 +18374,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -19121,7 +19107,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -19158,7 +19143,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -19400,7 +19384,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -19513,7 +19496,7 @@
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O352" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
-      <formula1>2026-07-01</formula1>
+      <formula1>2026-7-1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19529,22 +19512,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O326"/>
+  <dimension ref="A1:O487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="14" customWidth="1" style="11" min="4" max="5"/>
-    <col width="16" customWidth="1" style="11" min="6" max="6"/>
-    <col width="24" customWidth="1" style="11" min="7" max="7"/>
-    <col width="15" customWidth="1" style="11" min="8" max="8"/>
-    <col width="20" customWidth="1" style="11" min="9" max="9"/>
-    <col width="19" customWidth="1" style="11" min="10" max="10"/>
-    <col width="16" customWidth="1" style="11" min="11" max="11"/>
-    <col width="30" customWidth="1" style="11" min="12" max="12"/>
-    <col width="17" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="18" customWidth="1" style="11" min="15" max="15"/>
+    <col width="14" customWidth="1" style="12" min="1" max="2"/>
+    <col width="16" customWidth="1" style="12" min="3" max="3"/>
+    <col width="14" customWidth="1" style="12" min="4" max="4"/>
+    <col width="23.21875" bestFit="1" customWidth="1" style="12" min="5" max="5"/>
+    <col width="16" customWidth="1" style="12" min="6" max="6"/>
+    <col width="24" customWidth="1" style="12" min="7" max="7"/>
+    <col width="15" customWidth="1" style="12" min="8" max="8"/>
+    <col width="20" customWidth="1" style="12" min="9" max="9"/>
+    <col width="19" customWidth="1" style="12" min="10" max="10"/>
+    <col width="16" customWidth="1" style="12" min="11" max="11"/>
+    <col width="30" customWidth="1" style="12" min="12" max="12"/>
+    <col width="17" customWidth="1" style="12" min="13" max="13"/>
+    <col width="30" customWidth="1" style="12" min="14" max="14"/>
+    <col width="18" customWidth="1" style="12" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32294,18 +32278,6504 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Boga</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>non_idp_NG002004_supp1</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Boga</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>non_idp_NG002004_supp2</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Boga</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>non_idp_NG002004_supp3</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>non_idp_NG002004_supp4</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Bangshika</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp12</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp8</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Dubange</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>non_idp_NG002009_supp1</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Ngbebogun</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>non_idp_NG002009_supp2</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>non_idp_NG002009_supp3</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>non_idp_NG002009_supp4</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>non_idp_NG008016_supp2</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Digil</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp1</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp10</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp11</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp2</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Hussari Tampul</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp4</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp5</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Garaha</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp9</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp3</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp4</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp5</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp8</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Abbaram</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>non_idp_NG008016_supp3</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Abbaram</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>non_idp_NG008016_supp4</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Ajiri</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>non_idp_NG008016_supp5</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Guyaku</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp13</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>non_idp_NG002007_supp14</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Gundo</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>non_idp_NG002016_supp1</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp11</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Kurunabasa Ngoshe Sama</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp12</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp14</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>non_idp_NG002004_supp7</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Dirbishi</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>non_idp_NG002015_supp1</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>non_idp_NG002015_supp2</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Bare</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>non_idp_NG002016_supp2</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Kpasham</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>non_idp_NG002016_supp3</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Gundo</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>non_idp_NG002016_supp4</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Kodomti</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>non_idp_NG002016_supp5</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Gwadabawa</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp1</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp2</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Namtari</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp3</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Yolde Kohi</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>non_idp_NG002021_supp1</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Bole Yolde Pate</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>non_idp_NG002021_supp2</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Ngurore</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>non_idp_NG002021_supp3</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Gongolong</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>non_idp_NG008013_supp1</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Old Maiduguri</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>non_idp_NG008013_supp2</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Dagona</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>non_idp_NG036001_supp1</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Sugum Tagali</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>non_idp_NG036001_supp3</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Sarkin Hausawa</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>non_idp_NG036001_supp4</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Dawayo</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>non_idp_NG036001_supp5</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Gambir Moduri</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>non_idp_NG036003_supp1</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Kukareta Warsala</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>non_idp_NG036003_supp2</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Sasawa / Kabaru</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>non_idp_NG036003_supp3</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Kukareta Warsala</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>non_idp_NG036003_supp5</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Damakasu</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>non_idp_NG036003_supp6</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Ninkisi / Wuro Ngiki</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>non_idp_NG002013_supp1</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Muchalla</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>non_idp_NG002014_supp1</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Muchalla</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>non_idp_NG002014_supp2</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp15</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp16</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp17</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp19</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp20</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Galtimari</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>non_idp_NG008013_supp3</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Sugum Tagali</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>non_idp_NG036001_supp2</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp4</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp5</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp6</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Jambutu</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>non_idp_NG002020_supp7</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Boga</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp1</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp2</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Kilange Funa</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp3</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Gombi North</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp4</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Gombi North</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp5</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Gombi</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Boga</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>idp_NG002004_supp6</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>idp_NG002007_supp1</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>idp_NG002007_supp2</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>idp_NG002007_supp3</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Bangshika</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>idp_NG002007_supp4</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Bangshika</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>idp_NG002007_supp5</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Opalo</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>idp_NG002009_supp1</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Gyawana</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>idp_NG002009_supp2</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>idp_NG002009_supp3</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Manjekin</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>idp_NG002011_supp1</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Maiha</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Humbutudi</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>idp_NG002011_supp2</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Bazza Margi</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>idp_NG002013_supp1</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Madzi</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>idp_NG002013_supp2</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Munkavachitta</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>idp_NG002013_supp3</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Michika 2</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>idp_NG002013_supp4</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Yelwa</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp1</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp2</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Kolere</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp3</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Kolere</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp4</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Lokuwa</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp5</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Sabon Layi</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp6</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Digil</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp7</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Mubi North</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Muchalla</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>idp_NG002014_supp8</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Mugulbu</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp1</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp2</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Nassarawo</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp3</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Nassarawo</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp4</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp5</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Gude</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp6</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp7</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Sabon Layi</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp8</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Mubi South</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Mujara</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>idp_NG002015_supp9</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Kodomti</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>idp_NG002016_supp1</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Numan 1</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>idp_NG002016_supp2</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Numan 3</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>idp_NG002016_supp3</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Numan</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Bare</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>idp_NG002016_supp4</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp1</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Karewa</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp2</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Ajiya</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp3</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Alkalawa</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp4</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Nassarawo</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp5</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Yelwa</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp6</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Yola North</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Doubeli</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>idp_NG002020_supp7</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Yola South</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Bole Yolde Pate</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>idp_NG002021_supp1</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp1</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp10</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp11</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp12</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp13</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp14</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp15</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp16</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Hausari Gaddamayo</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp2</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp3</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Hausari Gaddamayo</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp4</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Hausari Gaddamayo</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp5</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Hausari Gaddamayo</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp6</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp7</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Bulabulin</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp8</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>idp_NG008011_supp9</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Old Maiduguri</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>idp_NG008013_supp1</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Dalori</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>idp_NG008013_supp2</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Jere</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Dusuman</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>idp_NG008013_supp3</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp10</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp5</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp9</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Sabon Gari</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp1</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Sabon Gari</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp2</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Gwio-Kura</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp3</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Katuzu</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp4</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Katuzu</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp5</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Lawan Fannami</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp6</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Lawan Musa</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp7</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Lawan Fannami</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp8</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Bade</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Lawan Fannami</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>idp_NG036001_supp9</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Damaturu Central</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>idp_NG036003_supp1</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Nayinawa</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>idp_NG036003_supp2</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Nayinawa</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>idp_NG036003_supp3</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Bindigari Pawari</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>idp_NG036003_supp4</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Yobe</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Damaturu</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Bindigari Pawari</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>idp_NG036003_supp5</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Jakana</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp1</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Jakana</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp2</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp3</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp4</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp6</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Auno</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp7</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Yale</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>idp_NG008016_supp8</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I326" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J326" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N326" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O326" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32572,13 +39042,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EB965D5-B48E-4FEC-BDF8-85F10B2DACAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156A2B4A-7E1D-4847-85FB-72809F0DC475}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760F032D-81B8-45D7-AF25-0839B9CBB247}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200BE77B-FB5F-4020-A229-AF1BF7005DAF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C528BE07-F79E-46E2-9885-0796D57EA7B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9595F93-B24C-4D9A-BBAB-BA40AFF35300}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O487" headerRowCount="1">
-  <autoFilter ref="A1:O487"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O491" headerRowCount="1">
+  <autoFilter ref="A1:O491"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -19512,7 +19512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O487"/>
+  <dimension ref="A1:O491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -32304,7 +32304,6 @@
           <t>non_idp_NG002004_supp1</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
           <t>6</t>
@@ -32342,7 +32341,6 @@
           <t>non_idp_NG002004_supp2</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>6</t>
@@ -32380,7 +32378,6 @@
           <t>non_idp_NG002004_supp3</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
           <t>6</t>
@@ -32418,7 +32415,6 @@
           <t>non_idp_NG002004_supp4</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>6</t>
@@ -32456,7 +32452,6 @@
           <t>non_idp_NG002007_supp12</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
           <t>6</t>
@@ -32494,7 +32489,6 @@
           <t>non_idp_NG002007_supp8</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>6</t>
@@ -32532,7 +32526,6 @@
           <t>non_idp_NG002009_supp1</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>6</t>
@@ -32570,7 +32563,6 @@
           <t>non_idp_NG002009_supp2</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>6</t>
@@ -32608,7 +32600,6 @@
           <t>non_idp_NG002009_supp3</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
           <t>6</t>
@@ -32646,7 +32637,6 @@
           <t>non_idp_NG002009_supp4</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>6</t>
@@ -32684,7 +32674,6 @@
           <t>non_idp_NG008016_supp2</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
           <t>6</t>
@@ -32722,7 +32711,6 @@
           <t>non_idp_NG002007_supp1</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>6</t>
@@ -32760,7 +32748,6 @@
           <t>non_idp_NG002007_supp10</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
           <t>6</t>
@@ -32798,7 +32785,6 @@
           <t>non_idp_NG002007_supp11</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>6</t>
@@ -32836,7 +32822,6 @@
           <t>non_idp_NG002007_supp2</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>6</t>
@@ -32874,7 +32859,6 @@
           <t>non_idp_NG002007_supp4</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>6</t>
@@ -32912,7 +32896,6 @@
           <t>non_idp_NG002007_supp5</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
           <t>6</t>
@@ -32950,7 +32933,6 @@
           <t>non_idp_NG002007_supp9</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>6</t>
@@ -32988,7 +32970,6 @@
           <t>non_idp_NG008011_supp3</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
           <t>6</t>
@@ -33026,7 +33007,6 @@
           <t>non_idp_NG008011_supp4</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
           <t>6</t>
@@ -33064,7 +33044,6 @@
           <t>non_idp_NG008011_supp5</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>6</t>
@@ -33102,7 +33081,6 @@
           <t>non_idp_NG008011_supp8</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>6</t>
@@ -33140,7 +33118,6 @@
           <t>non_idp_NG008016_supp3</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>6</t>
@@ -33178,7 +33155,6 @@
           <t>non_idp_NG008016_supp4</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>6</t>
@@ -33216,7 +33192,6 @@
           <t>non_idp_NG008016_supp5</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
           <t>6</t>
@@ -33254,7 +33229,6 @@
           <t>non_idp_NG002007_supp13</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>6</t>
@@ -33292,7 +33266,6 @@
           <t>non_idp_NG002007_supp14</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
       <c r="G353" t="inlineStr">
         <is>
           <t>6</t>
@@ -33330,7 +33303,6 @@
           <t>non_idp_NG002016_supp1</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
           <t>6</t>
@@ -33368,7 +33340,6 @@
           <t>non_idp_NG008011_supp11</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
           <t>6</t>
@@ -33406,7 +33377,6 @@
           <t>non_idp_NG008011_supp12</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>6</t>
@@ -33444,7 +33414,6 @@
           <t>non_idp_NG008011_supp14</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
           <t>6</t>
@@ -33482,7 +33451,6 @@
           <t>non_idp_NG002004_supp7</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>6</t>
@@ -33520,7 +33488,6 @@
           <t>non_idp_NG002015_supp1</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
           <t>6</t>
@@ -33558,7 +33525,6 @@
           <t>non_idp_NG002015_supp2</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>6</t>
@@ -33596,7 +33562,6 @@
           <t>non_idp_NG002016_supp2</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>6</t>
@@ -33634,7 +33599,6 @@
           <t>non_idp_NG002016_supp3</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>6</t>
@@ -33672,7 +33636,6 @@
           <t>non_idp_NG002016_supp4</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr">
         <is>
           <t>6</t>
@@ -33710,7 +33673,6 @@
           <t>non_idp_NG002016_supp5</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>6</t>
@@ -33748,7 +33710,6 @@
           <t>non_idp_NG002020_supp1</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr">
         <is>
           <t>6</t>
@@ -33786,7 +33747,6 @@
           <t>non_idp_NG002020_supp2</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr">
         <is>
           <t>6</t>
@@ -33824,7 +33784,6 @@
           <t>non_idp_NG002020_supp3</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
           <t>6</t>
@@ -33862,7 +33821,6 @@
           <t>non_idp_NG002021_supp1</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>6</t>
@@ -33900,7 +33858,6 @@
           <t>non_idp_NG002021_supp2</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr">
         <is>
           <t>6</t>
@@ -33938,7 +33895,6 @@
           <t>non_idp_NG002021_supp3</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>6</t>
@@ -33976,7 +33932,6 @@
           <t>non_idp_NG008013_supp1</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
           <t>6</t>
@@ -34014,7 +33969,6 @@
           <t>non_idp_NG008013_supp2</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>6</t>
@@ -34052,7 +34006,6 @@
           <t>non_idp_NG036001_supp1</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
           <t>6</t>
@@ -34090,7 +34043,6 @@
           <t>non_idp_NG036001_supp3</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>6</t>
@@ -34128,7 +34080,6 @@
           <t>non_idp_NG036001_supp4</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
           <t>6</t>
@@ -34166,7 +34117,6 @@
           <t>non_idp_NG036001_supp5</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
           <t>6</t>
@@ -34204,7 +34154,6 @@
           <t>non_idp_NG036003_supp1</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
           <t>6</t>
@@ -34242,7 +34191,6 @@
           <t>non_idp_NG036003_supp2</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
           <t>6</t>
@@ -34280,7 +34228,6 @@
           <t>non_idp_NG036003_supp3</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
           <t>6</t>
@@ -34318,7 +34265,6 @@
           <t>non_idp_NG036003_supp5</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>6</t>
@@ -34356,7 +34302,6 @@
           <t>non_idp_NG036003_supp6</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>6</t>
@@ -34394,7 +34339,6 @@
           <t>non_idp_NG002013_supp1</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>6</t>
@@ -34432,7 +34376,6 @@
           <t>non_idp_NG002014_supp1</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
           <t>6</t>
@@ -34470,7 +34413,6 @@
           <t>non_idp_NG002014_supp2</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>6</t>
@@ -34508,7 +34450,6 @@
           <t>non_idp_NG008011_supp15</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
           <t>6</t>
@@ -34546,7 +34487,6 @@
           <t>non_idp_NG008011_supp16</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
           <t>6</t>
@@ -34584,7 +34524,6 @@
           <t>non_idp_NG008011_supp17</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr">
         <is>
           <t>6</t>
@@ -34622,7 +34561,6 @@
           <t>non_idp_NG008011_supp19</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
           <t>6</t>
@@ -34660,7 +34598,6 @@
           <t>non_idp_NG008011_supp20</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
           <t>6</t>
@@ -34698,7 +34635,6 @@
           <t>non_idp_NG008013_supp3</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>6</t>
@@ -34736,7 +34672,6 @@
           <t>non_idp_NG036001_supp2</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>6</t>
@@ -34774,7 +34709,6 @@
           <t>non_idp_NG002020_supp4</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
           <t>6</t>
@@ -34812,7 +34746,6 @@
           <t>non_idp_NG002020_supp5</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
           <t>6</t>
@@ -34850,7 +34783,6 @@
           <t>non_idp_NG002020_supp6</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>6</t>
@@ -34888,7 +34820,6 @@
           <t>non_idp_NG002020_supp7</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>6</t>
@@ -38764,18 +38695,170 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Adamawa</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Lamurde</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Gyawana</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>non_idp_NG002009_supp5</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp9</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Gwoza</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Pulka Bokko</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>non_idp_NG008011_supp10</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Konduga</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Dalori</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>non_idp_NG008016_supp6</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O487" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -38784,271 +38867,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156A2B4A-7E1D-4847-85FB-72809F0DC475}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200BE77B-FB5F-4020-A229-AF1BF7005DAF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9595F93-B24C-4D9A-BBAB-BA40AFF35300}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -28108,6 +28108,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -28330,6 +28335,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -29051,6 +29061,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -29604,6 +29619,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -29789,6 +29809,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -32980,6 +33005,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -33054,6 +33084,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -33091,6 +33126,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -33128,6 +33168,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -33165,6 +33210,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -33202,6 +33252,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -33350,6 +33405,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -33387,6 +33447,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -33424,6 +33489,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -38721,7 +38791,6 @@
           <t>non_idp_NG002009_supp5</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
           <t>6</t>
@@ -38759,7 +38828,6 @@
           <t>non_idp_NG008011_supp9</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
           <t>6</t>
@@ -38797,7 +38865,6 @@
           <t>non_idp_NG008011_supp10</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr">
         <is>
           <t>6</t>
@@ -38835,7 +38902,6 @@
           <t>non_idp_NG008016_supp6</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr">
         <is>
           <t>6</t>

--- a/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/NRC_accessibility_report.xlsx
@@ -38933,4 +38933,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD534DF8-1B0D-4DF1-AF99-64FB03CC1F36}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6C299E8-D3F5-4C54-8225-B3CF042E5662}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B57821A-E291-476C-8ACC-306119EA9C50}"/>
 </file>